--- a/Labs/Lab09/Lab9Rubric_CS295N.xlsx
+++ b/Labs/Lab09/Lab9Rubric_CS295N.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repos\CS295N-CourseMaterials\Labs\Lab09\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repos\CS295N-296N-Repos\CS295N-CourseMaterials\Labs\Lab09\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D07043-6525-4216-AAF3-B56FACB7BB73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE294E8-5740-441C-8E17-D1CE0899F52B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31764" yWindow="4224" windowWidth="12636" windowHeight="11844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15036" yWindow="4356" windowWidth="15048" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rubric" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="23">
   <si>
     <t>Actual</t>
   </si>
@@ -51,12 +51,6 @@
     <t>Search by date</t>
   </si>
   <si>
-    <t>Lab 8 Rubric</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (used to be lab 9)</t>
-  </si>
-  <si>
     <t>LINQ queries</t>
   </si>
   <si>
@@ -90,10 +84,25 @@
     <t>Good work on the seed data and searches!</t>
   </si>
   <si>
-    <t>Lab 8: Seed Data and Linq</t>
-  </si>
-  <si>
     <t>Code style and best practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (used to be lab 9, then 8, now 6)</t>
+  </si>
+  <si>
+    <t>Lab 6 Rubric</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Lab 6: Seed Data and Linq</t>
+  </si>
+  <si>
+    <t>(Old lab 9 which became 8, now 6)</t>
   </si>
 </sst>
 </file>
@@ -670,20 +679,20 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -744,9 +753,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -784,7 +793,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -890,7 +899,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1032,7 +1041,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1052,27 +1061,27 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18">
       <c r="A1" s="4" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B1" s="12"/>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="C2" s="14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C4">
         <v>12</v>
@@ -1083,13 +1092,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" s="4"/>
     </row>
     <row r="7" spans="1:7" ht="17.399999999999999">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1098,7 +1107,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1124,7 +1133,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B11" s="13">
         <f>SUM(C6:C10)</f>
@@ -1139,7 +1148,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C13" s="11">
         <v>8</v>
@@ -1148,7 +1157,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -1335,32 +1344,35 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="18"/>
+      <c r="A2" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="15"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="18"/>
+      <c r="A3" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="15"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>1</v>
@@ -1370,12 +1382,12 @@
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>12</v>
@@ -1383,20 +1395,27 @@
       <c r="C5">
         <v>12</v>
       </c>
-      <c r="E5" s="15"/>
+      <c r="E5" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="E6" s="16"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
     </row>
     <row r="7" spans="1:6" ht="17.399999999999999">
       <c r="A7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="17"/>
+        <v>5</v>
+      </c>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8">
         <v>4</v>
@@ -1404,11 +1423,16 @@
       <c r="C8">
         <v>4</v>
       </c>
-      <c r="E8" s="16"/>
+      <c r="E8" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B9">
         <v>4</v>
@@ -1416,7 +1440,12 @@
       <c r="C9">
         <v>4</v>
       </c>
-      <c r="E9" s="15"/>
+      <c r="E9" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="11" t="s">
@@ -1428,7 +1457,12 @@
       <c r="C10">
         <v>4</v>
       </c>
-      <c r="E10" s="16"/>
+      <c r="E10" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
@@ -1440,22 +1474,29 @@
       <c r="C11">
         <v>4</v>
       </c>
-      <c r="E11" s="15"/>
+      <c r="E11" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3"/>
       <c r="C12" s="13"/>
-      <c r="E12" s="16"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
     </row>
     <row r="13" spans="1:6">
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
-      <c r="E13" s="16"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" s="11">
         <v>8</v>
@@ -1464,11 +1505,16 @@
         <v>8</v>
       </c>
       <c r="D14" s="11"/>
-      <c r="E14" s="16"/>
+      <c r="E14" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B15">
         <v>4</v>
@@ -1476,12 +1522,18 @@
       <c r="C15">
         <v>4</v>
       </c>
-      <c r="E15" s="16"/>
+      <c r="E15" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="E16" s="16"/>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="7" t="s">
         <v>2</v>
       </c>
@@ -1493,54 +1545,55 @@
         <f>SUM(C5:C15)</f>
         <v>40</v>
       </c>
-      <c r="E17" s="15"/>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="7"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:6">
       <c r="E19" s="5"/>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:6">
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:6">
       <c r="A21" s="2"/>
       <c r="B21" s="3"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:6">
       <c r="A22" s="1"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:6">
       <c r="A23" s="8"/>
       <c r="B23" s="9"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:6">
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:6">
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:6">
       <c r="A26" s="4"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:6">
       <c r="A27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:6">
       <c r="A29" s="4"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:6">
       <c r="E31" s="5"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:6">
       <c r="A32" s="4"/>
       <c r="E32" s="5"/>
     </row>
